--- a/Project_ETF/ETF_Investment_Portfolio/00919/ETF_Investment_Portfolio_20260828.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/00919/ETF_Investment_Portfolio_20260828.xlsx
@@ -1327,17 +1327,17 @@
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>1319</t>
+          <t>6890</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>東陽</t>
+          <t>來億-KY</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>27,850,000</t>
+          <t>13,510,000</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
@@ -1349,17 +1349,17 @@
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>6890</t>
+          <t>1319</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>來億-KY</t>
+          <t>東陽</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>13,510,000</t>
+          <t>27,850,000</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr">
@@ -1371,17 +1371,17 @@
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>6670</t>
+          <t>1210</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>復盛應用</t>
+          <t>大成</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>8,010,000</t>
+          <t>41,370,000</t>
         </is>
       </c>
       <c r="D56" s="4" t="inlineStr">
@@ -1393,17 +1393,17 @@
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>1210</t>
+          <t>6670</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>大成</t>
+          <t>復盛應用</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>41,370,000</t>
+          <t>8,010,000</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
@@ -1459,17 +1459,17 @@
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>4915</t>
+          <t>2211</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>致伸</t>
+          <t>長榮鋼</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>29,006,000</t>
+          <t>20,540,000</t>
         </is>
       </c>
       <c r="D60" s="4" t="inlineStr">
@@ -1481,17 +1481,17 @@
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>2211</t>
+          <t>4915</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>長榮鋼</t>
+          <t>致伸</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>20,540,000</t>
+          <t>29,006,000</t>
         </is>
       </c>
       <c r="D61" s="4" t="inlineStr">
